--- a/04_DESIGN_TABLES/DesignTable_5502.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_5502.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O52"/>
+  <dimension ref="A1:P52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -541,6 +541,11 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -549,7 +554,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>0.89</v>
+        <v>0.78</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>0.66</v>
@@ -586,10 +591,14 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr"/>
+          <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3; N@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N1458 = 0.780 (table had 0.89) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 3 open): N@DRIVE 0.89 -&gt; OMi 0.780 (Items!N1458, M109)</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -931,7 +940,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -939,7 +948,11 @@
           <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3</t>
         </is>
       </c>
-      <c r="M9" s="3" t="inlineStr"/>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on W@REF=0.75~0.750; D@BORE=0.28~0.281</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1106,7 +1119,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -1114,7 +1127,11 @@
           <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3</t>
         </is>
       </c>
-      <c r="M12" s="3" t="inlineStr"/>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on W@REF=0.88~0.875; D@BORE=0.28~0.281</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1339,7 +1356,7 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -1347,7 +1364,11 @@
           <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3</t>
         </is>
       </c>
-      <c r="M16" s="3" t="inlineStr"/>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on W@REF=0.88~0.875; D@BORE=0.41~0.406</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1456,7 +1477,7 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
@@ -1464,7 +1485,11 @@
           <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3</t>
         </is>
       </c>
-      <c r="M18" s="3" t="inlineStr"/>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on W@REF=0.88~0.875; D@BORE=0.41~0.406</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1602,7 +1627,7 @@
         <v>1.47</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>0.875</v>
@@ -1636,10 +1661,14 @@
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3; W@REF: OMi WebsitePartsInfo2026.xlsx Items!R1469 Hex Flat = 0.875 (table had 1.06) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="M21" s="3" t="inlineStr"/>
+          <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3; W@REF: OMi WebsitePartsInfo2026.xlsx Items!R1469 Hex Flat = 0.875 (table had 1.06) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; N1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1469 = 1.010 (table had 1) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 3 open): N1@DRIVE 1 -&gt; OMi 1.010 (Items!P1469, M110)</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1719,7 +1748,7 @@
         <v>1.47</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>0.875</v>
@@ -1753,10 +1782,14 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3; W@REF: OMi WebsitePartsInfo2026.xlsx Items!R1470 Hex Flat = 0.875 (table had 1.06) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="M23" s="3" t="inlineStr"/>
+          <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3; W@REF: OMi WebsitePartsInfo2026.xlsx Items!R1470 Hex Flat = 0.875 (table had 1.06) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; N1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1470 = 1.020 (table had 1.01) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 3 open): N1@DRIVE 1.01 -&gt; OMi 1.020 (Items!P1470, M110)</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1865,7 +1898,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
@@ -1873,7 +1906,11 @@
           <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3</t>
         </is>
       </c>
-      <c r="M25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on W@REF=1.06~1.062; D@BORE=0.53~0.531</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1982,7 +2019,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
@@ -1990,7 +2027,11 @@
           <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3</t>
         </is>
       </c>
-      <c r="M27" s="3" t="inlineStr"/>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on W@REF=1.31~1.312; D@BORE=0.53~0.531</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -2215,7 +2256,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
@@ -2225,12 +2266,17 @@
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23)</t>
+          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | Brennan TFA TFA-p031-t03: agrees on N@DRIVE, N1@DRIVE, W@REF, D@BORE</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>5502-12-12-FG</t>
         </is>
       </c>
     </row>
@@ -2418,10 +2464,10 @@
         <v>1.97</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>1.63</v>
+        <v>1.312</v>
       </c>
       <c r="E35" s="3" t="n">
         <v>0.9399999999999999</v>
@@ -2457,12 +2503,17 @@
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23)</t>
+          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | OMi dims first (user 2026-09-25): W@REF: OMi WebsitePartsInfo2026.xlsx Items!R1477 = 1.312 (table had 1.63) | Brennan TFA TFA-p031-t03: agrees on N@DRIVE, W@REF, D@BORE; DIFFERS on N1@DRIVE 1.39 vs Brennan N1 LGTH 1.360 (built to the dimension source, s6) | A19-style (user 2026-10-18 'yes, apply the 7 pending OMi values'): N1@DRIVE 1.39 -&gt; 1.36</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>5502-16-12-FG</t>
         </is>
       </c>
     </row>
@@ -2563,7 +2614,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
@@ -2573,12 +2624,17 @@
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23)</t>
+          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | Brennan TFA TFA-p031-t03: agrees on N@DRIVE, N1@DRIVE, W@REF, D@BORE</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>5502-16-16-FG</t>
         </is>
       </c>
     </row>
@@ -2763,7 +2819,7 @@
         </is>
       </c>
       <c r="B41" s="4" t="n">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="C41" s="4" t="n">
         <v>1.7</v>
@@ -2800,12 +2856,12 @@
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3</t>
+          <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3; N@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N1481 = 2.380 (table had 2.75) [user 2026-10-18 A19]</t>
         </is>
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>N 2.75 vs non-FG 2.38 (FG &gt; non-FG by .37, unusual) - as-printed</t>
+          <t>N 2.75 vs non-FG 2.38 (FG &gt; non-FG by .37, unusual) - as-printed | A19 (user 2026-10-18, group 3 open): N@DRIVE 2.75 -&gt; OMi 2.380 (Items!N1481, M109)</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -2942,7 +2998,7 @@
         </is>
       </c>
       <c r="B44" s="4" t="n">
-        <v>3.05</v>
+        <v>2.64</v>
       </c>
       <c r="C44" s="4" t="n">
         <v>2.08</v>
@@ -2979,12 +3035,12 @@
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3</t>
+          <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3; N@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N1484 = 2.640 (table had 3.05) [user 2026-10-18 A19]</t>
         </is>
       </c>
       <c r="M44" s="4" t="inlineStr">
         <is>
-          <t>N 3.05 vs non-FG 2.70 - as-printed</t>
+          <t>N 3.05 vs non-FG 2.70 - as-printed | A19 (user 2026-10-18, group 3 open): N@DRIVE 3.05 -&gt; OMi 2.640 (Items!N1484, M109)</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3153,7 +3209,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="L47" s="4" t="inlineStr">
@@ -3163,7 +3219,7 @@
       </c>
       <c r="M47" s="4" t="inlineStr">
         <is>
-          <t>tap drill 2.20 vs non-FG 2.19 same thread - as-printed</t>
+          <t>tap drill 2.20 vs non-FG 2.19 same thread - as-printed | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on W@REF=2.81~2.812; D@BORE=1.94~1.938</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3241,24 +3297,50 @@
           <t>5502-02-04-FG</t>
         </is>
       </c>
+      <c r="B49" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.54</v>
+      </c>
       <c r="I49" t="inlineStr">
         <is>
           <t>5502-02-04-FG</t>
         </is>
       </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>1/8-27 (male) x 1/4-18 (female) NPTF</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5502-02-04 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5502-02-04 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): N@DRIVE: Brennan TFA catalog p.31 table TFA-p031-t03 "5502-FG MP-FP 90 DEG ELBOW STREET ELBOW" row 5502-02-04-FG col "N LGTH" = "0.900" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 457.2, page verified True) [Brennan = yes 2026-10-18] - axis crossing to the male NPTF tip (column mapping: REPORT.md, table 5502); = OMi WebsitePartsInfo2026 Items!N1459 "M 1 Size" = 0.900 (same value; OMi and Brennan count as one source); N1@DRIVE: Brennan TFA catalog p.31 table TFA-p031-t03 "5502-FG MP-FP 90 DEG ELBOW STREET ELBOW" row 5502-02-04-FG col "N1 LGTH" = "0.880" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 457.2, page verified True) [Brennan = yes 2026-10-18] - axis crossing to the female NPTF port face (column mapping: REPORT.md, table 5502); = OMi WebsitePartsInfo2026 Items!P1459 "L 1 Size" = 0.880 (same value; OMi and Brennan count as one source); W@REF: Brennan TFA catalog p.31 table TFA-p031-t03 "5502-FG MP-FP 90 DEG ELBOW STREET ELBOW" row 5502-02-04-FG col "Y FLATS" = "0.750" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 457.2, page verified True) [Brennan = yes 2026-10-18] - forged body flats (column mapping: REPORT.md, table 5502); = OMi WebsitePartsInfo2026 Items!R1459 "Hex Flat" = 0.750 (same value; OMi and Brennan count as one source); D@BORE: Brennan TFA catalog p.31 table TFA-p031-t03 "5502-FG MP-FP 90 DEG ELBOW STREET ELBOW" row 5502-02-04-FG col "A1 DRILL" = "0.188" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 457.2, page verified True) [Brennan = yes 2026-10-18] - male end drill (column mapping: REPORT.md, table 5502); = OMi WebsitePartsInfo2026 Items!S1459 "Side 1 ID" = 0.188 (same value; OMi and Brennan count as one source); TAPDRILL@BORE: end library: tap drill of the -04 female NPTF port = 0.43 (gen_straight2 FPT[4] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A; = Air-Way's per-size tap drill of OPEN_QUESTIONS A1) [Q-TRANSFER-TAPDRILL = A1 answered YES 2026-10-18 (00_DOCS/ANSWERS_2026-10-18.md): Air-Way per-size tap drill on existing families]; THDMAJ_A1@DRIVE: end library: pipe OD of the -02 NPTF thread = 0.405 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[2], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A2@DRIVE: end library: pipe OD of the -04 NPTF thread = 0.54 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[4], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Threads: thread callouts from the part number dashes in the format of the table's other rows; = Brennan TFA-p031-t03 thread columns (A1 NPTF 1/8-27, A2 NPTF 1/4-18) and OMi Items Side 1 / 2 / 3 Thread</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5502-02-04 dims are NOT assumed; confirm before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5502-02-04 dims are NOT assumed; confirm before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog (= OMi Items, one source), end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3269,6 +3351,11 @@
       <c r="O49" t="inlineStr">
         <is>
           <t>5502-02-04-FG</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -3278,24 +3365,50 @@
           <t>5502-06-08-FG</t>
         </is>
       </c>
+      <c r="B50" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="C50" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.84</v>
+      </c>
       <c r="I50" t="inlineStr">
         <is>
           <t>5502-06-08-FG</t>
         </is>
       </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>3/8-18 (male) x 1/2-14 (female) NPTF</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5502-06-08 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5502-06-08 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): N@DRIVE: Brennan TFA catalog p.31 table TFA-p031-t03 "5502-FG MP-FP 90 DEG ELBOW STREET ELBOW" row 5502-06-08-FG col "N LGTH" = "1.280" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 527.8, page verified True) [Brennan = yes 2026-10-18] - axis crossing to the male NPTF tip (column mapping: REPORT.md, table 5502); = OMi WebsitePartsInfo2026 Items!N1468 "M 1 Size" = 1.280 (same value; OMi and Brennan count as one source); N1@DRIVE: Brennan TFA catalog p.31 table TFA-p031-t03 "5502-FG MP-FP 90 DEG ELBOW STREET ELBOW" row 5502-06-08-FG col "N1 LGTH" = "1.230" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 527.8, page verified True) [Brennan = yes 2026-10-18] - axis crossing to the female NPTF port face (column mapping: REPORT.md, table 5502); = OMi WebsitePartsInfo2026 Items!P1468 "L 1 Size" = 1.230 (same value; OMi and Brennan count as one source); W@REF: Brennan TFA catalog p.31 table TFA-p031-t03 "5502-FG MP-FP 90 DEG ELBOW STREET ELBOW" row 5502-06-08-FG col "Y FLATS" = "1.062" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 527.8, page verified True) [Brennan = yes 2026-10-18] - forged body flats (column mapping: REPORT.md, table 5502); = OMi WebsitePartsInfo2026 Items!R1468 "Hex Flat" = 1.062 (same value; OMi and Brennan count as one source); D@BORE: Brennan TFA catalog p.31 table TFA-p031-t03 "5502-FG MP-FP 90 DEG ELBOW STREET ELBOW" row 5502-06-08-FG col "A1 DRILL" = "0.406" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 527.8, page verified True) [Brennan = yes 2026-10-18] - male end drill (column mapping: REPORT.md, table 5502); = OMi WebsitePartsInfo2026 Items!S1468 "Side 1 ID" = 0.406 (same value; OMi and Brennan count as one source); TAPDRILL@BORE: end library: tap drill of the -08 female NPTF port = 0.7 (gen_straight2 FPT[8] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A; = Air-Way's per-size tap drill of OPEN_QUESTIONS A1) [Q-TRANSFER-TAPDRILL = A1 answered YES 2026-10-18 (00_DOCS/ANSWERS_2026-10-18.md): Air-Way per-size tap drill on existing families]; THDMAJ_A1@DRIVE: end library: pipe OD of the -06 NPTF thread = 0.675 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[6], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A2@DRIVE: end library: pipe OD of the -08 NPTF thread = 0.84 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[8], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Threads: thread callouts from the part number dashes in the format of the table's other rows; = Brennan TFA-p031-t03 thread columns (A1 NPTF 3/8-18, A2 NPTF 1/2-14) and OMi Items Side 1 / 2 / 3 Thread</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5502-06-08 dims are NOT assumed; confirm before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5502-06-08 dims are NOT assumed; confirm before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog (= OMi Items, one source), end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -3306,6 +3419,11 @@
       <c r="O50" t="inlineStr">
         <is>
           <t>5502-06-08-FG</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -3315,24 +3433,50 @@
           <t>5502-12-08-FG</t>
         </is>
       </c>
+      <c r="B51" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="C51" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="D51" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G51" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.84</v>
+      </c>
       <c r="I51" t="inlineStr">
         <is>
           <t>5502-12-08-FG</t>
         </is>
       </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>3/4-14 (male) x 1/2-14 (female) NPTF</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5502-12-08 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5502-12-08 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): N@DRIVE: Brennan TFA catalog p.31 table TFA-p031-t03 "5502-FG MP-FP 90 DEG ELBOW STREET ELBOW" row 5502-12-08-FG col "N LGTH" = "1.590" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 588.2, page verified True) [Brennan = yes 2026-10-18] - axis crossing to the male NPTF tip (column mapping: REPORT.md, table 5502); = OMi WebsitePartsInfo2026 Items!N1474 "M 1 Size" = 1.590 (same value; OMi and Brennan count as one source); N1@DRIVE: Brennan TFA catalog p.31 table TFA-p031-t03 "5502-FG MP-FP 90 DEG ELBOW STREET ELBOW" row 5502-12-08-FG col "N1 LGTH" = "1.230" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 588.2, page verified True) [Brennan = yes 2026-10-18] - axis crossing to the female NPTF port face (column mapping: REPORT.md, table 5502); = OMi WebsitePartsInfo2026 Items!P1474 "L 1 Size" = 1.230 (same value; OMi and Brennan count as one source); W@REF: Brennan TFA catalog p.31 table TFA-p031-t03 "5502-FG MP-FP 90 DEG ELBOW STREET ELBOW" row 5502-12-08-FG col "Y FLATS" = "1.062" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 588.2, page verified True) [Brennan = yes 2026-10-18] - forged body flats (column mapping: REPORT.md, table 5502); = OMi WebsitePartsInfo2026 Items!R1474 "Hex Flat" = 1.062 (same value; OMi and Brennan count as one source); D@BORE: Brennan TFA catalog p.31 table TFA-p031-t03 "5502-FG MP-FP 90 DEG ELBOW STREET ELBOW" row 5502-12-08-FG col "A1 DRILL" = "0.719" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 588.2, page verified True) [Brennan = yes 2026-10-18] - male end drill (column mapping: REPORT.md, table 5502); = OMi WebsitePartsInfo2026 Items!S1474 "Side 1 ID" = 0.719 (same value; OMi and Brennan count as one source); TAPDRILL@BORE: end library: tap drill of the -08 female NPTF port = 0.7 (gen_straight2 FPT[8] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A; = Air-Way's per-size tap drill of OPEN_QUESTIONS A1) [Q-TRANSFER-TAPDRILL = A1 answered YES 2026-10-18 (00_DOCS/ANSWERS_2026-10-18.md): Air-Way per-size tap drill on existing families]; THDMAJ_A1@DRIVE: end library: pipe OD of the -12 NPTF thread = 1.05 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[12], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A2@DRIVE: end library: pipe OD of the -08 NPTF thread = 0.84 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[8], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Threads: thread callouts from the part number dashes in the format of the table's other rows; = Brennan TFA-p031-t03 thread columns (A1 NPTF 3/4-14, A2 NPTF 1/2-14) and OMi Items Side 1 / 2 / 3 Thread</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5502-12-08 dims are NOT assumed; confirm before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5502-12-08 dims are NOT assumed; confirm before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog (= OMi Items, one source), end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -3343,6 +3487,11 @@
       <c r="O51" t="inlineStr">
         <is>
           <t>5502-12-08-FG</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -3352,24 +3501,50 @@
           <t>5502-20-16-FG</t>
         </is>
       </c>
+      <c r="B52" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="C52" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="G52" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="H52" t="n">
+        <v>1.315</v>
+      </c>
       <c r="I52" t="inlineStr">
         <is>
           <t>5502-20-16-FG</t>
         </is>
       </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>1 1/4-11 1/2 (male) x 1-11 1/2 (female) NPTF</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5502-20-16 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5502-20-16 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): N@DRIVE: Brennan TFA catalog p.31 table TFA-p031-t03 "5502-FG MP-FP 90 DEG ELBOW STREET ELBOW" row 5502-20-16-FG col "N LGTH" = "2.380" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 648.7, page verified True) [Brennan = yes 2026-10-18] - axis crossing to the male NPTF tip (column mapping: REPORT.md, table 5502); = OMi WebsitePartsInfo2026 Items!N1480 "M 1 Size" = 2.380 (same value; OMi and Brennan count as one source); N1@DRIVE: Brennan TFA catalog p.31 table TFA-p031-t03 "5502-FG MP-FP 90 DEG ELBOW STREET ELBOW" row 5502-20-16-FG col "N1 LGTH" = "1.620" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 648.7, page verified True) [Brennan = yes 2026-10-18] - axis crossing to the female NPTF port face (column mapping: REPORT.md, table 5502); = OMi WebsitePartsInfo2026 Items!P1480 "L 1 Size" = 1.620 (same value; OMi and Brennan count as one source); W@REF: Brennan TFA catalog p.31 table TFA-p031-t03 "5502-FG MP-FP 90 DEG ELBOW STREET ELBOW" row 5502-20-16-FG col "Y FLATS" = "1.625" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 648.7, page verified True) [Brennan = yes 2026-10-18] - forged body flats (column mapping: REPORT.md, table 5502); = OMi WebsitePartsInfo2026 Items!R1480 "Hex Flat" = 1.625 (same value; OMi and Brennan count as one source); D@BORE: Brennan TFA catalog p.31 table TFA-p031-t03 "5502-FG MP-FP 90 DEG ELBOW STREET ELBOW" row 5502-20-16-FG col "A1 DRILL" = "1.250" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 648.7, page verified True) [Brennan = yes 2026-10-18] - male end drill (column mapping: REPORT.md, table 5502); = OMi WebsitePartsInfo2026 Items!S1480 "Side 1 ID" = 1.250 (same value; OMi and Brennan count as one source); TAPDRILL@BORE: end library: tap drill of the -16 female NPTF port = 1.14 (gen_straight2 FPT[16] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A; = Air-Way's per-size tap drill of OPEN_QUESTIONS A1) [Q-TRANSFER-TAPDRILL = A1 answered YES 2026-10-18 (00_DOCS/ANSWERS_2026-10-18.md): Air-Way per-size tap drill on existing families]; THDMAJ_A1@DRIVE: end library: pipe OD of the -20 NPTF thread = 1.66 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[20], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A2@DRIVE: end library: pipe OD of the -16 NPTF thread = 1.315 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[16], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Threads: thread callouts from the part number dashes in the format of the table's other rows; = Brennan TFA-p031-t03 thread columns (A1 NPTF 1-1/4-11-1/2, A2 NPTF 1-11-1/2) and OMi Items Side 1 / 2 / 3 Thread</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5502-20-16 dims are NOT assumed; confirm before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5502-20-16 dims are NOT assumed; confirm before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog (= OMi Items, one source), end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -3380,6 +3555,11 @@
       <c r="O52" t="inlineStr">
         <is>
           <t>5502-20-16-FG</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>

--- a/04_DESIGN_TABLES/DesignTable_5502.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_5502.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>0.78</v>
+        <v>0.89</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>0.66</v>
@@ -591,12 +591,12 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3; N@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N1458 = 0.780 (table had 0.89) [user 2026-10-18 A19]</t>
+          <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3; N@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N1458 = 0.780 (table had 0.89) [user 2026-10-18 A19]; N@DRIVE: Air-Way 0.89 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.78) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 3 open): N@DRIVE 0.89 -&gt; OMi 0.780 (Items!N1458, M109)</t>
+          <t>A19 (user 2026-10-18, group 3 open): N@DRIVE 0.89 -&gt; OMi 0.780 (Items!N1458, M109) | 2026-10-20 Air-Way first: N@DRIVE OMi/Brennan 0.78 -&gt; Air-Way 0.89</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -855,7 +855,7 @@
         <v>0.67</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>0.28</v>
@@ -886,10 +886,14 @@
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3; W@REF: OMi WebsitePartsInfo2026.xlsx Items!R1461 Hex Flat = 0.562 (table had 0.75) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr"/>
+          <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3; W@REF: OMi WebsitePartsInfo2026.xlsx Items!R1461 Hex Flat = 0.562 (table had 0.75) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; W@REF: Air-Way 0.75 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.562) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: W@REF OMi/Brennan 0.562 -&gt; Air-Way 0.75</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1627,10 +1631,10 @@
         <v>1.47</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>0.875</v>
+        <v>1.06</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>0.53</v>
@@ -1661,12 +1665,12 @@
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3; W@REF: OMi WebsitePartsInfo2026.xlsx Items!R1469 Hex Flat = 0.875 (table had 1.06) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; N1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1469 = 1.010 (table had 1) [user 2026-10-18 A19]</t>
+          <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3; W@REF: OMi WebsitePartsInfo2026.xlsx Items!R1469 Hex Flat = 0.875 (table had 1.06) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; N1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1469 = 1.010 (table had 1) [user 2026-10-18 A19]; N1@DRIVE: Air-Way 1 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.01) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; W@REF: Air-Way 1.06 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.875) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 3 open): N1@DRIVE 1 -&gt; OMi 1.010 (Items!P1469, M110)</t>
+          <t>A19 (user 2026-10-18, group 3 open): N1@DRIVE 1 -&gt; OMi 1.010 (Items!P1469, M110) | 2026-10-20 Air-Way first: N1@DRIVE OMi/Brennan 1.01 -&gt; Air-Way 1 | 2026-10-20 Air-Way first: W@REF OMi/Brennan 0.875 -&gt; Air-Way 1.06</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1748,10 +1752,10 @@
         <v>1.47</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.875</v>
+        <v>1.06</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>0.53</v>
@@ -1782,12 +1786,12 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3; W@REF: OMi WebsitePartsInfo2026.xlsx Items!R1470 Hex Flat = 0.875 (table had 1.06) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; N1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1470 = 1.020 (table had 1.01) [user 2026-10-18 A19]</t>
+          <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3; W@REF: OMi WebsitePartsInfo2026.xlsx Items!R1470 Hex Flat = 0.875 (table had 1.06) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; N1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1470 = 1.020 (table had 1.01) [user 2026-10-18 A19]; N1@DRIVE: Air-Way 1.01 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.02) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; W@REF: Air-Way 1.06 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.875) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 3 open): N1@DRIVE 1.01 -&gt; OMi 1.020 (Items!P1470, M110)</t>
+          <t>A19 (user 2026-10-18, group 3 open): N1@DRIVE 1.01 -&gt; OMi 1.020 (Items!P1470, M110) | 2026-10-20 Air-Way first: N1@DRIVE OMi/Brennan 1.02 -&gt; Air-Way 1.01 | 2026-10-20 Air-Way first: W@REF OMi/Brennan 0.875 -&gt; Air-Way 1.06</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2464,10 +2468,10 @@
         <v>1.97</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>1.312</v>
+        <v>1.63</v>
       </c>
       <c r="E35" s="3" t="n">
         <v>0.9399999999999999</v>
@@ -2498,12 +2502,12 @@
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3</t>
+          <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3; N1@DRIVE: Air-Way 1.39 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.36) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; W@REF: Air-Way 1.63 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.312) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | OMi dims first (user 2026-09-25): W@REF: OMi WebsitePartsInfo2026.xlsx Items!R1477 = 1.312 (table had 1.63) | Brennan TFA TFA-p031-t03: agrees on N@DRIVE, W@REF, D@BORE; DIFFERS on N1@DRIVE 1.39 vs Brennan N1 LGTH 1.360 (built to the dimension source, s6) | A19-style (user 2026-10-18 'yes, apply the 7 pending OMi values'): N1@DRIVE 1.39 -&gt; 1.36</t>
+          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | OMi dims first (user 2026-09-25): W@REF: OMi WebsitePartsInfo2026.xlsx Items!R1477 = 1.312 (table had 1.63) | Brennan TFA TFA-p031-t03: agrees on N@DRIVE, W@REF, D@BORE; DIFFERS on N1@DRIVE 1.39 vs Brennan N1 LGTH 1.360 (built to the dimension source, s6) | A19-style (user 2026-10-18 'yes, apply the 7 pending OMi values'): N1@DRIVE 1.39 -&gt; 1.36 | 2026-10-20 Air-Way first: N1@DRIVE OMi/Brennan 1.36 -&gt; Air-Way 1.39 | 2026-10-20 Air-Way first: W@REF OMi/Brennan 1.312 -&gt; Air-Way 1.63</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2819,7 +2823,7 @@
         </is>
       </c>
       <c r="B41" s="4" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="C41" s="4" t="n">
         <v>1.7</v>
@@ -2856,12 +2860,12 @@
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3; N@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N1481 = 2.380 (table had 2.75) [user 2026-10-18 A19]</t>
+          <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3; N@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N1481 = 2.380 (table had 2.75) [user 2026-10-18 A19]; N@DRIVE: Air-Way 2.75 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.38) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>N 2.75 vs non-FG 2.38 (FG &gt; non-FG by .37, unusual) - as-printed | A19 (user 2026-10-18, group 3 open): N@DRIVE 2.75 -&gt; OMi 2.380 (Items!N1481, M109)</t>
+          <t>N 2.75 vs non-FG 2.38 (FG &gt; non-FG by .37, unusual) - as-printed | A19 (user 2026-10-18, group 3 open): N@DRIVE 2.75 -&gt; OMi 2.380 (Items!N1481, M109) | 2026-10-20 Air-Way first: N@DRIVE OMi/Brennan 2.38 -&gt; Air-Way 2.75</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -2998,7 +3002,7 @@
         </is>
       </c>
       <c r="B44" s="4" t="n">
-        <v>2.64</v>
+        <v>3.05</v>
       </c>
       <c r="C44" s="4" t="n">
         <v>2.08</v>
@@ -3035,12 +3039,12 @@
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3; N@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N1484 = 2.640 (table had 3.05) [user 2026-10-18 A19]</t>
+          <t>Air-Way s128 only (double-pass 46 rows; page footer claimed 47); female NPTF per ANSI B1.20.3; N@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N1484 = 2.640 (table had 3.05) [user 2026-10-18 A19]; N@DRIVE: Air-Way 3.05 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.64) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="M44" s="4" t="inlineStr">
         <is>
-          <t>N 3.05 vs non-FG 2.70 - as-printed | A19 (user 2026-10-18, group 3 open): N@DRIVE 3.05 -&gt; OMi 2.640 (Items!N1484, M109)</t>
+          <t>N 3.05 vs non-FG 2.70 - as-printed | A19 (user 2026-10-18, group 3 open): N@DRIVE 3.05 -&gt; OMi 2.640 (Items!N1484, M109) | 2026-10-20 Air-Way first: N@DRIVE OMi/Brennan 2.64 -&gt; Air-Way 3.05</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
